--- a/input/ProyectosBogota.xlsx
+++ b/input/ProyectosBogota.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomarval-my.sharepoint.com/personal/cpulgarin_marval_com_co/Documents/0. Personal/7. Empleo/7.4 Madurez Lean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{110482E1-758B-4879-A3B1-A35920DDCC5B}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA10BDE-0C49-4962-B24B-F5085A60DC6D}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E3F5C54B-12F1-4F71-BE4C-2ADA05C14CFA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F5C54B-12F1-4F71-BE4C-2ADA05C14CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="56">
   <si>
     <t>Sucursal</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>SABADO</t>
-  </si>
-  <si>
-    <t>JUEVES/VIERNES</t>
   </si>
   <si>
     <t>MIERCOLES</t>
@@ -761,7 +758,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -776,7 +773,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -791,7 +788,7 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -821,7 +818,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -836,7 +833,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -857,7 +854,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="5">
         <v>0.33333333333333331</v>
@@ -910,7 +907,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -970,7 +967,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -985,7 +982,7 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1017,13 +1014,13 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5">
         <v>0.33333333333333331</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" s="5">
         <v>0.58333333333333337</v>
@@ -1042,7 +1039,7 @@
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -1055,7 +1052,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1070,7 +1067,7 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1085,7 +1082,7 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E22" s="5">
         <v>0.41666666666666669</v>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1121,7 +1118,7 @@
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1172,7 +1169,7 @@
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1204,11 +1201,11 @@
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -1238,7 +1235,7 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1274,7 +1271,7 @@
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1306,7 +1303,7 @@
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" s="5">
         <v>0.58333333333333337</v>
@@ -1323,7 +1320,7 @@
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1338,7 +1335,7 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="5">
         <v>0.58333333333333337</v>
@@ -1359,7 +1356,7 @@
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1401,7 +1398,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G40" s="5">
         <v>0.45833333333333331</v>
@@ -1416,7 +1413,7 @@
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>

--- a/input/ProyectosBogota.xlsx
+++ b/input/ProyectosBogota.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomarval-my.sharepoint.com/personal/cpulgarin_marval_com_co/Documents/0. Personal/7. Empleo/7.4 Madurez Lean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA10BDE-0C49-4962-B24B-F5085A60DC6D}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761DBE1D-88B1-4DCD-B866-2D8B31744CAD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F5C54B-12F1-4F71-BE4C-2ADA05C14CFA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="56">
   <si>
     <t>Sucursal</t>
   </si>
@@ -1223,8 +1223,12 @@
       <c r="E30" s="5">
         <v>0.39583333333333331</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="F30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">

--- a/input/ProyectosBogota.xlsx
+++ b/input/ProyectosBogota.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomarval-my.sharepoint.com/personal/cpulgarin_marval_com_co/Documents/0. Personal/7. Empleo/7.4 Madurez Lean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761DBE1D-88B1-4DCD-B866-2D8B31744CAD}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="8_{4456A4CA-A1D7-4AF1-AA2A-73D85DC9AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8089CC5-F3AD-4527-A1D8-7060C3EFF312}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F5C54B-12F1-4F71-BE4C-2ADA05C14CFA}"/>
   </bookViews>
